--- a/docs/detail-design/09_GiaHan.xlsx
+++ b/docs/detail-design/09_GiaHan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="176">
   <si>
     <t>SWEET HOME · DETAIL DESIGN · GIA HẠN / CHUYỂN PHÒNG</t>
   </si>
@@ -135,6 +135,12 @@
     <t>Tạo mới.</t>
   </si>
   <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Phòng còn khách Quá giờ / Chờ xác nhận trả không còn nằm trong danh sách phòng chuyển được.</t>
+  </si>
+  <si>
     <t>Ảnh 1. Gia hạn tại phòng (giữ được phòng)</t>
   </si>
   <si>
@@ -498,10 +504,10 @@
     <t>Phòng chuyển được</t>
   </si>
   <si>
-    <t>Khi không giữ được phòng: phòng khác, đủ 4 mức giá hiện hành bằng phòng đang ở, đang nhận đặt, không Chờ dọn, không có chặng (đơn chưa huỷ) giao [giờ trả hiện tại, giờ trả mới + 1 tiếng); sắp theo số phòng; kèm giờ nhận đơn kế tiếp của phòng đó (freeUntil).</t>
-  </si>
-  <si>
-    <t>Lưu ý (hành vi hiện tại): kiểm tra "trống" theo khung giờ hẹn của các chặng. Phòng còn khách Quá giờ / Chờ xác nhận trả (chặng đã hết giờ hẹn nhưng chưa trả phòng) vẫn có thể nằm trong danh sách phòng chuyển được — đã báo lại để xem xét.</t>
+    <t>Khi không giữ được phòng: phòng khác, đủ 4 mức giá hiện hành bằng phòng đang ở, đang nhận đặt, không Chờ dọn, không có chặng (đơn chưa huỷ) giao [giờ trả hiện tại, giờ trả mới + 1 tiếng), không còn khách Quá giờ / Chờ xác nhận trả; sắp theo số phòng; kèm giờ nhận đơn kế tiếp của phòng đó (freeUntil).</t>
+  </si>
+  <si>
+    <t>Phòng còn khách chưa trả: chặng hiện tại của đơn Quá giờ / Chờ xác nhận trả (đã hết giờ hẹn nhưng chưa trả phòng) coi là kéo dài tới bây giờ + 1 tiếng, nên phòng đó không nằm trong danh sách phòng chuyển được (RentalOrderRepository.findOverlapping, tham số busyUntil).</t>
   </si>
   <si>
     <t>3. Xác nhận — POST /api/orders/{id}/extend</t>
@@ -733,7 +739,7 @@
       <xdr:row>43</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6400800" cy="10591800"/>
+    <xdr:ext cx="6400800" cy="9248775"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 2">
@@ -769,7 +775,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>102</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="6400800" cy="9686925"/>
@@ -1176,7 +1182,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG21"/>
+  <dimension ref="B1:AG22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1907,8 +1913,50 @@
       <c r="AF21" s="3"/>
       <c r="AG21" s="3"/>
     </row>
+    <row r="22" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="43">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="I2:AG2"/>
@@ -1948,6 +1996,10 @@
     <mergeCell ref="E21:H21"/>
     <mergeCell ref="I21:M21"/>
     <mergeCell ref="N21:AG21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="I22:M22"/>
+    <mergeCell ref="N22:AG22"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
@@ -1958,7 +2010,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG102"/>
+  <dimension ref="B1:AG95"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1967,7 +2019,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -2003,7 +2055,7 @@
     </row>
     <row r="43" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B43" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -2037,47 +2089,47 @@
       <c r="AF43" s="4"/>
       <c r="AG43" s="4"/>
     </row>
-    <row r="102" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B102" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
-      <c r="E102" s="4"/>
-      <c r="F102" s="4"/>
-      <c r="G102" s="4"/>
-      <c r="H102" s="4"/>
-      <c r="I102" s="4"/>
-      <c r="J102" s="4"/>
-      <c r="K102" s="4"/>
-      <c r="L102" s="4"/>
-      <c r="M102" s="4"/>
-      <c r="N102" s="4"/>
-      <c r="O102" s="4"/>
-      <c r="P102" s="4"/>
-      <c r="Q102" s="4"/>
-      <c r="R102" s="4"/>
-      <c r="S102" s="4"/>
-      <c r="T102" s="4"/>
-      <c r="U102" s="4"/>
-      <c r="V102" s="4"/>
-      <c r="W102" s="4"/>
-      <c r="X102" s="4"/>
-      <c r="Y102" s="4"/>
-      <c r="Z102" s="4"/>
-      <c r="AA102" s="4"/>
-      <c r="AB102" s="4"/>
-      <c r="AC102" s="4"/>
-      <c r="AD102" s="4"/>
-      <c r="AE102" s="4"/>
-      <c r="AF102" s="4"/>
-      <c r="AG102" s="4"/>
+    <row r="95" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B95" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C95" s="4"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
+      <c r="L95" s="4"/>
+      <c r="M95" s="4"/>
+      <c r="N95" s="4"/>
+      <c r="O95" s="4"/>
+      <c r="P95" s="4"/>
+      <c r="Q95" s="4"/>
+      <c r="R95" s="4"/>
+      <c r="S95" s="4"/>
+      <c r="T95" s="4"/>
+      <c r="U95" s="4"/>
+      <c r="V95" s="4"/>
+      <c r="W95" s="4"/>
+      <c r="X95" s="4"/>
+      <c r="Y95" s="4"/>
+      <c r="Z95" s="4"/>
+      <c r="AA95" s="4"/>
+      <c r="AB95" s="4"/>
+      <c r="AC95" s="4"/>
+      <c r="AD95" s="4"/>
+      <c r="AE95" s="4"/>
+      <c r="AF95" s="4"/>
+      <c r="AG95" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="B43:AG43"/>
-    <mergeCell ref="B102:AG102"/>
+    <mergeCell ref="B95:AG95"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing r:id="rId1"/>
@@ -2098,7 +2150,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -2134,10 +2186,10 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
@@ -2148,22 +2200,22 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P2" s="5"/>
       <c r="Q2" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R2" s="5"/>
       <c r="S2" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
@@ -2171,12 +2223,12 @@
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
       <c r="Y2" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>
       <c r="AB2" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
@@ -2189,33 +2241,33 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P3" s="3"/>
       <c r="Q3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R3" s="3"/>
       <c r="S3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
@@ -2223,12 +2275,12 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
@@ -2241,33 +2293,33 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
@@ -2275,12 +2327,12 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
@@ -2293,33 +2345,33 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
@@ -2327,12 +2379,12 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
@@ -2345,33 +2397,33 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
@@ -2379,12 +2431,12 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
@@ -2397,33 +2449,33 @@
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
@@ -2431,12 +2483,12 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
       <c r="AB7" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
@@ -2449,33 +2501,33 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R8" s="3"/>
       <c r="S8" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
@@ -2483,12 +2535,12 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
       <c r="AB8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
@@ -2501,33 +2553,33 @@
         <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R9" s="3"/>
       <c r="S9" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
@@ -2535,12 +2587,12 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
       <c r="AB9" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
@@ -2553,33 +2605,33 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -2587,12 +2639,12 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
       <c r="AB10" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
@@ -2605,33 +2657,33 @@
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R11" s="3"/>
       <c r="S11" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
@@ -2639,12 +2691,12 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
@@ -2657,33 +2709,33 @@
         <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R12" s="3"/>
       <c r="S12" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
@@ -2691,12 +2743,12 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
       <c r="AB12" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
@@ -2709,33 +2761,33 @@
         <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R13" s="3"/>
       <c r="S13" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
@@ -2743,12 +2795,12 @@
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
       <c r="AB13" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
@@ -2761,33 +2813,33 @@
         <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R14" s="3"/>
       <c r="S14" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
@@ -2795,12 +2847,12 @@
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
       <c r="AB14" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
@@ -2813,33 +2865,33 @@
         <v>13</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R15" s="3"/>
       <c r="S15" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
@@ -2847,12 +2899,12 @@
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
       <c r="AB15" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
@@ -2862,7 +2914,7 @@
     </row>
     <row r="17" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -2898,10 +2950,10 @@
     </row>
     <row r="18" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
@@ -2912,22 +2964,22 @@
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
       <c r="O18" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P18" s="5"/>
       <c r="Q18" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R18" s="5"/>
       <c r="S18" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
@@ -2935,12 +2987,12 @@
       <c r="W18" s="5"/>
       <c r="X18" s="5"/>
       <c r="Y18" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Z18" s="5"/>
       <c r="AA18" s="5"/>
       <c r="AB18" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AC18" s="5"/>
       <c r="AD18" s="5"/>
@@ -2953,33 +3005,33 @@
         <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P19" s="3"/>
       <c r="Q19" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R19" s="3"/>
       <c r="S19" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
@@ -2987,12 +3039,12 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
@@ -3005,33 +3057,33 @@
         <v>15</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="P20" s="3"/>
       <c r="Q20" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="R20" s="3"/>
       <c r="S20" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
@@ -3039,12 +3091,12 @@
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
       <c r="AB20" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
@@ -3057,33 +3109,33 @@
         <v>16</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P21" s="3"/>
       <c r="Q21" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R21" s="3"/>
       <c r="S21" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
@@ -3091,12 +3143,12 @@
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
       <c r="Y21" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
       <c r="AB21" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
@@ -3109,33 +3161,33 @@
         <v>17</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P22" s="3"/>
       <c r="Q22" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R22" s="3"/>
       <c r="S22" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
@@ -3143,12 +3195,12 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
       <c r="Y22" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
       <c r="AB22" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AC22" s="3"/>
       <c r="AD22" s="3"/>
@@ -3158,7 +3210,7 @@
     </row>
     <row r="24" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -3194,10 +3246,10 @@
     </row>
     <row r="25" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -3208,22 +3260,22 @@
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
       <c r="O25" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P25" s="5"/>
       <c r="Q25" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R25" s="5"/>
       <c r="S25" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="T25" s="5"/>
       <c r="U25" s="5"/>
@@ -3231,12 +3283,12 @@
       <c r="W25" s="5"/>
       <c r="X25" s="5"/>
       <c r="Y25" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Z25" s="5"/>
       <c r="AA25" s="5"/>
       <c r="AB25" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AC25" s="5"/>
       <c r="AD25" s="5"/>
@@ -3249,33 +3301,33 @@
         <v>18</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P26" s="3"/>
       <c r="Q26" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R26" s="3"/>
       <c r="S26" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
@@ -3283,12 +3335,12 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3"/>
       <c r="AB26" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AC26" s="3"/>
       <c r="AD26" s="3"/>
@@ -3301,33 +3353,33 @@
         <v>19</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P27" s="3"/>
       <c r="Q27" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R27" s="3"/>
       <c r="S27" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
@@ -3335,12 +3387,12 @@
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3"/>
       <c r="AB27" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AC27" s="3"/>
       <c r="AD27" s="3"/>
@@ -3353,33 +3405,33 @@
         <v>20</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P28" s="3"/>
       <c r="Q28" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R28" s="3"/>
       <c r="S28" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
@@ -3387,12 +3439,12 @@
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3"/>
       <c r="AB28" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AC28" s="3"/>
       <c r="AD28" s="3"/>
@@ -3608,7 +3660,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3644,7 +3696,7 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -3680,10 +3732,10 @@
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -3718,10 +3770,10 @@
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -3756,10 +3808,10 @@
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -3794,7 +3846,7 @@
     </row>
     <row r="7" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -3830,7 +3882,7 @@
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -3838,7 +3890,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
@@ -3868,7 +3920,7 @@
     </row>
     <row r="9" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -3876,7 +3928,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -3906,7 +3958,7 @@
     </row>
     <row r="10" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -3914,7 +3966,7 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -3944,7 +3996,7 @@
     </row>
     <row r="11" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -3952,7 +4004,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
@@ -3982,7 +4034,7 @@
     </row>
     <row r="12" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -3990,7 +4042,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
@@ -4020,7 +4072,7 @@
     </row>
     <row r="13" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -4028,7 +4080,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
@@ -4058,7 +4110,7 @@
     </row>
     <row r="14" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -4066,7 +4118,7 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
@@ -4094,9 +4146,9 @@
       <c r="AF14" s="3"/>
       <c r="AG14" s="3"/>
     </row>
-    <row r="15" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="15" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -4104,7 +4156,7 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
@@ -4134,7 +4186,7 @@
     </row>
     <row r="16" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
@@ -4170,7 +4222,7 @@
     </row>
     <row r="18" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -4206,10 +4258,10 @@
     </row>
     <row r="19" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
@@ -4244,10 +4296,10 @@
     </row>
     <row r="20" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B20" s="7" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
@@ -4282,10 +4334,10 @@
     </row>
     <row r="21" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -4320,10 +4372,10 @@
     </row>
     <row r="22" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B22" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
@@ -4358,10 +4410,10 @@
     </row>
     <row r="23" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B23" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
@@ -4396,10 +4448,10 @@
     </row>
     <row r="24" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B24" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
@@ -4434,10 +4486,10 @@
     </row>
     <row r="25" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
@@ -4472,7 +4524,7 @@
     </row>
     <row r="27" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
